--- a/SUEWSPrepare/Input/SUEWS_init.xlsx
+++ b/SUEWSPrepare/Input/SUEWS_init.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" tabRatio="867" activeTab="15"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="867" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Example DO NOT CHANGE POSITION" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="Water Use (Automatic)" sheetId="15" r:id="rId15"/>
     <sheet name="ESTM Coefficients" sheetId="17" r:id="rId16"/>
   </sheets>
-  <calcPr calcId="122211" concurrentCalc="0"/>
+  <calcPr calcId="122211"/>
 </workbook>
 </file>
 
@@ -130,15 +130,6 @@
     <t>Snow clearing profile (Weekdays)</t>
   </si>
   <si>
-    <t>SUEWS_AnthropogenicHeat</t>
-  </si>
-  <si>
-    <t>SUEWS_AnthropogenicHeat.txt</t>
-  </si>
-  <si>
-    <t>Modelling anthropogenic heat flux</t>
-  </si>
-  <si>
     <t>SUEWS_Irrigation</t>
   </si>
   <si>
@@ -174,11 +165,20 @@
   <si>
     <t>ESTM Coefficients (codes will be added to the final output according to file input not what is selected in this tab)</t>
   </si>
+  <si>
+    <t>SUEWS_AnthropogenicEmission</t>
+  </si>
+  <si>
+    <t>SUEWS_AnthropogenicEmission.txt</t>
+  </si>
+  <si>
+    <t>Modelling anthropogenic heat flux and emissions</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -219,6 +219,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -267,7 +270,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -302,7 +305,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -512,17 +515,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
-    <col min="2" max="2" width="29.140625" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" customWidth="1"/>
-    <col min="4" max="4" width="41.140625" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" customWidth="1"/>
+    <col min="2" max="2" width="29.109375" customWidth="1"/>
+    <col min="3" max="3" width="17.88671875" customWidth="1"/>
+    <col min="4" max="4" width="41.109375" customWidth="1"/>
     <col min="5" max="5" width="41" customWidth="1"/>
-    <col min="6" max="6" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -539,10 +542,10 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -559,7 +562,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -570,16 +573,16 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -593,7 +596,7 @@
         <v>660</v>
       </c>
       <c r="F1">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -604,17 +607,17 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>29</v>
       </c>
@@ -631,10 +634,10 @@
         <v>660</v>
       </c>
       <c r="F1">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -651,7 +654,7 @@
         <v>660</v>
       </c>
       <c r="F2">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -662,16 +665,44 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.5546875" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" customWidth="1"/>
+    <col min="3" max="3" width="32.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1">
+        <v>661</v>
+      </c>
+      <c r="F1">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -682,38 +713,10 @@
         <v>35</v>
       </c>
       <c r="E1">
-        <v>661</v>
-      </c>
-      <c r="F1">
-        <v>53</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1">
         <v>660</v>
       </c>
       <c r="F1">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -724,17 +727,17 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="45" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>29</v>
       </c>
@@ -742,7 +745,7 @@
         <v>30</v>
       </c>
       <c r="C1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D1">
         <v>1</v>
@@ -751,10 +754,10 @@
         <v>660</v>
       </c>
       <c r="F1">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -762,7 +765,7 @@
         <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -771,7 +774,7 @@
         <v>660</v>
       </c>
       <c r="F2">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -782,13 +785,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="1" width="21.5546875" customWidth="1"/>
+    <col min="2" max="2" width="30.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>29</v>
       </c>
@@ -796,7 +799,7 @@
         <v>30</v>
       </c>
       <c r="C1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D1">
         <v>1</v>
@@ -805,10 +808,10 @@
         <v>660</v>
       </c>
       <c r="F1">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -816,7 +819,7 @@
         <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -825,7 +828,7 @@
         <v>660</v>
       </c>
       <c r="F2">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -836,23 +839,23 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="103" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C1" t="s">
-        <v>47</v>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" t="s">
+        <v>44</v>
       </c>
       <c r="F1">
         <v>85</v>
@@ -866,17 +869,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -893,7 +896,7 @@
         <v>661</v>
       </c>
       <c r="F1">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -904,17 +907,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -931,7 +934,7 @@
         <v>662</v>
       </c>
       <c r="F1">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -942,9 +945,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -961,7 +964,7 @@
         <v>661</v>
       </c>
       <c r="F1">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -972,14 +975,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -996,7 +999,7 @@
         <v>662</v>
       </c>
       <c r="F1">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1007,9 +1010,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -1026,7 +1029,7 @@
         <v>663</v>
       </c>
       <c r="F1">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1037,9 +1040,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -1056,7 +1059,7 @@
         <v>663</v>
       </c>
       <c r="F1">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1067,12 +1070,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="9.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>22</v>
       </c>
@@ -1086,7 +1091,7 @@
         <v>661</v>
       </c>
       <c r="F1">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1097,9 +1102,12 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -1113,7 +1121,7 @@
         <v>200</v>
       </c>
       <c r="F1">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
